--- a/output/testing_result_databaru/evaluation_testing_80_20.xlsx
+++ b/output/testing_result_databaru/evaluation_testing_80_20.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,70 +429,80 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Jenis Rule</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Jenis Rule Label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Support Training</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Confidence Training</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Lift Training</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Kategori Training</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Antecedent Support</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Consequent Support</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Lift</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Kategori Rule</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Count Antecedent</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Count Consequent</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Count Both</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Status Pengujian</t>
         </is>
@@ -509,50 +519,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>0.01455696202531646</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.6388888888888888</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>1.979302832244008</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2.380165289256198</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>11</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>121</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>8</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -569,50 +589,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.5333333333333333</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>1.652287581699346</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.03282828282828283</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>2.265734265734265</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>13</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>121</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>9</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -629,50 +659,60 @@
           <t>waktu_Malam</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>1.750692520775623</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.2575757575757576</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0.01515151515151515</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.5</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>1.941176470588235</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>12</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>102</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>6</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -689,50 +729,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>0.01772151898734177</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>0.4444444444444445</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>1.462962962962963</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.04797979797979798</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.3080808080808081</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.02525252525252525</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.5263157894736842</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>1.708369283865401</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>19</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>122</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>10</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -749,50 +799,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>0.01265822784810127</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>0.5128205128205128</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>1.081784259354353</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>0.01767676767676768</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>1.673913043478261</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>9</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>184</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>7</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -809,50 +869,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>0.01708860759493671</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>1.054739652870494</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.01767676767676768</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>1.673913043478261</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>9</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>184</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>7</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -869,50 +939,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>0.01518987341772152</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>0.4799999999999999</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>1.012550066755674</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.03535353535353535</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.02525252525252525</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>1.537267080745342</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>14</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>184</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -929,50 +1009,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>0.01139240506329114</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>0.4864864864864865</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>1.507154213036566</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.01262626262626263</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>1.487603305785124</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>11</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>121</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>5</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -989,50 +1079,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>0.01075949367088608</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>0.4473684210526316</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>1.385964912280702</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.01262626262626263</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>1.363636363636364</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>12</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>121</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1049,50 +1149,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>0.04113924050632911</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>0.6074766355140186</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>1.281459391337983</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.06313131313131314</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.03787878787878788</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.6</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>1.291304347826087</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>25</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>184</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>15</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1109,50 +1219,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>0.02215189873417722</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>1.171932947633882</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.04797979797979798</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.5789473684210527</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>1.245995423340961</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
         <v>19</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>184</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>11</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1169,50 +1289,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>0.01075949367088608</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>0.4047619047619048</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>1.324065858227349</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.0505050505050505</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.3232323232323233</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.4</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>1.2375</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
         <v>20</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>128</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>8</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1229,50 +1359,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>0.6153846153846153</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>2.013059404363752</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>0.01262626262626263</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.3232323232323233</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.005050505050505051</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>1.2375</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
         <v>5</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>128</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1289,50 +1429,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>0.02025316455696203</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>0.653061224489796</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>1.377619138443094</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>0.03535353535353535</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>1.229813664596273</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
         <v>14</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>184</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>8</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1349,50 +1499,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>0.4848484848484849</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>1.586046803438108</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.3232323232323233</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.375</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>1.16015625</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>8</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>128</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>3</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1409,50 +1569,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>0.05126582278481013</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>0.5159235668789809</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>1.088330087675287</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>0.1136363636363636</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.05808080808080808</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.5111111111111111</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>1.1</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
         <v>45</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>184</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>23</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1469,50 +1639,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>0.64</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>1.350066755674233</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.005050505050505051</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>1.076086956521739</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
         <v>4</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>184</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1529,50 +1709,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>0.1474683544303798</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>0.4854166666666667</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>1.023976412995105</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>0.3080808080808081</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.1515151515151515</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.4918032786885246</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>1.058446186742694</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
         <v>122</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>184</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>60</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1589,50 +1779,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>0.03164556962025317</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>0.4807692307692308</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>1.014172743144706</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>0.08838383838383838</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>0.04292929292929293</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.4857142857142857</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>1.045341614906832</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
         <v>35</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>184</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>17</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1649,50 +1849,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>0.01582278481012658</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>0.5208333333333334</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>1.70376121463078</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.3232323232323233</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>1.03125</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>12</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>128</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>4</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1709,50 +1919,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
         <v>0.15</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>0.4906832298136645</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>1.035086118966075</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>0.3232323232323233</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.1515151515151515</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.46875</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>1.00883152173913</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
         <v>128</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>184</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>60</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1769,50 +1989,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
         <v>0.01075949367088608</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>0.5151515151515151</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>1.595959595959596</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>0.02525252525252525</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.3</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.9818181818181817</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>10</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>121</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>3</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1829,50 +2059,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
         <v>0.01645569620253165</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>0.5416666666666667</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>1.142634623943035</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.01262626262626263</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.8967391304347827</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>12</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>184</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>5</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1889,50 +2129,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>0.4102564102564102</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>1.270990447461036</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.3055555555555556</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.8925619834710743</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>11</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>121</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>3</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1949,50 +2199,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
         <v>0.01455696202531646</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>0.6388888888888888</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>1.347722889778965</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="I26" t="n">
         <v>0.04292929292929293</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.01767676767676768</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.4117647058823529</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.8861892583120204</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>17</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>184</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>7</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2009,50 +2269,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
         <v>0.01329113924050633</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>0.5</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>1.054739652870494</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>0.0505050505050505</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.4</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.8608695652173913</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>20</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>184</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2069,50 +2339,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
         <v>0.0120253164556962</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>0.5135135135135135</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>1.083246129975102</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>0.02525252525252525</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>0.0101010101010101</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.8608695652173913</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>10</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>184</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>4</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2129,50 +2409,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
         <v>0.01518987341772152</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>0.4210526315789474</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>1.385964912280702</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.3080808080808081</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.005050505050505051</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.7213114754098361</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>9</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>122</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>2</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2189,50 +2479,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
         <v>0.01518987341772152</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>0.5853658536585366</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>1.234817154580091</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.7173913043478261</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>9</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>184</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>3</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2249,50 +2549,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
         <v>0.02278481012658228</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>0.4675324675324675</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>1.52940227474389</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>0.03535353535353535</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.3232323232323233</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.2142857142857143</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.6629464285714285</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>14</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>128</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2309,50 +2619,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
         <v>0.01139240506329114</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>1.150625075858721</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>0.02525252525252525</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.3</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.6456521739130434</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>10</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>184</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>3</v>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2369,50 +2689,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
         <v>0.01075949367088608</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>0.53125</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>1.737836438923395</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>0.01262626262626263</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.3232323232323233</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>0.002525252525252525</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.2</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.61875</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>5</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>128</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2429,50 +2759,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
         <v>0.01708860759493671</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>0.5510204081632654</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>1.162366148061361</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>0.01767676767676768</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.005050505050505051</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.6149068322981366</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>7</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>184</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>2</v>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2489,50 +2829,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
         <v>0.01329113924050633</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>0.6</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>1.265687583444593</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.005050505050505051</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.25</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.5380434782608696</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>8</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>184</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>2</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2549,50 +2899,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
         <v>0.01139240506329114</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>0.45</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>1.472049689440994</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.3232323232323233</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>0.005050505050505051</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.5156249999999999</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>12</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>128</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>2</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2609,50 +2969,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>0.01392405063291139</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>0.5116279069767442</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>1.079268482007017</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>0.03787878787878788</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.4646464646464646</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.005050505050505051</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.2869565217391304</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>15</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>184</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>2</v>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2669,50 +3039,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>0.4102564102564102</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>1.35042735042735</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.3080808080808081</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>11</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>122</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0</v>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
